--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/ConchV1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7864077669902912</v>
+        <v>0.7572815533980582</v>
       </c>
       <c r="C8" t="n">
         <v>0.845360824742268</v>
@@ -622,7 +622,7 @@
         <v>0.8217821782178217</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7986555496304524</v>
+        <v>0.7913739962323941</v>
       </c>
     </row>
     <row r="9">
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7643939393939394</v>
+        <v>0.775</v>
       </c>
       <c r="C9" t="n">
         <v>0.7481684981684982</v>
@@ -644,7 +644,7 @@
         <v>0.7546816479400749</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7578436300712803</v>
+        <v>0.7604951452227955</v>
       </c>
     </row>
     <row r="10">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6820987654320987</v>
+        <v>0.665280124788769</v>
       </c>
       <c r="C10" t="n">
         <v>0.712052246190382</v>
@@ -666,7 +666,7 @@
         <v>0.6817226890756303</v>
       </c>
       <c r="F10" t="n">
-        <v>0.68730293186265</v>
+        <v>0.6830982717018177</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8111590554956251</v>
+        <v>0.7896524264272528</v>
       </c>
       <c r="C11" t="n">
         <v>0.8554599594810471</v>
@@ -688,7 +688,7 @@
         <v>0.842686579582328</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8195668118522038</v>
+        <v>0.8141901545851108</v>
       </c>
     </row>
     <row r="12">
@@ -698,10 +698,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8075757575757575</v>
+        <v>0.8613636363636363</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7756410256410257</v>
+        <v>0.7847985347985348</v>
       </c>
       <c r="D12" t="n">
         <v>0.808695652173913</v>
@@ -710,7 +710,7 @@
         <v>0.7874531835205993</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7948414047278239</v>
+        <v>0.8105777517141709</v>
       </c>
     </row>
     <row r="13">
@@ -721,27 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>[[66, 22], [3, 12]]</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[[74, 10], [5, 8]]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>[[67, 25], [4, 16]]</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>[[75, 14], [4, 8]]</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>[[70, 18], [4, 11]]</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>[[74, 10], [5, 8]]</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[[67, 25], [4, 16]]</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[[75, 14], [4, 8]]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[[72, 17], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7986555496304524</v>
+        <v>0.7913739962323941</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03931336557339455</v>
+        <v>0.04339319692046178</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7578436300712803</v>
+        <v>0.7604951452227955</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006819764915948197</v>
+        <v>0.01011618901252959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.68730293186265</v>
+        <v>0.6830982717018177</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01471198144564183</v>
+        <v>0.01769868361723394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8195668118522038</v>
+        <v>0.8141901545851108</v>
       </c>
       <c r="M3" t="n">
-        <v>0.03337069894087268</v>
+        <v>0.03592687192805422</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7948414047278239</v>
+        <v>0.8105777517141709</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01394044730663963</v>
+        <v>0.03074923599551218</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[72, 17], [4, 11]]</t>
+          <t>[[70, 18], [4, 11]]</t>
         </is>
       </c>
     </row>
